--- a/public/sap-reporting/expansion-150-downloads/EXT-CO20-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO20-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rcb182abfc56849bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R96af685b536042bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R8e449c10bca549a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R497e34dc839c4738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R087103b4535747f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R6e66c6f707274510"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -509,7 +509,7 @@
         <x:v>66.66666667</x:v>
       </x:c>
       <x:c r="P7" s="2" t="str">
-        <x:v>-200.00</x:v>
+        <x:v>-20.00</x:v>
       </x:c>
       <x:c r="Q7" s="2" t="str">
         <x:v>OPEN</x:v>
@@ -810,7 +810,7 @@
         <x:v>66.66666667</x:v>
       </x:c>
       <x:c r="P2" s="2" t="str">
-        <x:v>-200.00</x:v>
+        <x:v>-20.00</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="str">
         <x:v>OPEN</x:v>
